--- a/pautas_excel/6 de Octubre.xlsx
+++ b/pautas_excel/6 de Octubre.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -85,17 +85,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E0B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0F0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0E0C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -156,14 +146,6 @@
       <left style="thin">
         <color rgb="00000000"/>
       </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
       <top style="thin">
         <color rgb="00000000"/>
       </top>
@@ -183,21 +165,28 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -214,10 +203,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00000000"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -278,17 +287,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="00000000"/>
       </left>
@@ -303,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -311,19 +309,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="20" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -332,69 +352,90 @@
     <xf numFmtId="20" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="20" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="20" fontId="1" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,23 +801,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.573109243697479" customWidth="1" min="1" max="1"/>
     <col width="74.75630252100839" customWidth="1" min="2" max="2"/>
-    <col width="63.46218487394958" customWidth="1" min="3" max="3"/>
-    <col width="5.378151260504202" customWidth="1" min="4" max="4"/>
-    <col width="16.56470588235294" customWidth="1" min="5" max="5"/>
-    <col width="10.1109243697479" customWidth="1" min="6" max="6"/>
-    <col width="9.89579831932773" customWidth="1" min="7" max="7"/>
+    <col width="32.16134453781513" customWidth="1" min="3" max="3"/>
+    <col width="31.30084033613445" customWidth="1" min="4" max="4"/>
+    <col width="5.378151260504202" customWidth="1" min="5" max="5"/>
+    <col width="8.067226890756302" customWidth="1" min="6" max="6"/>
+    <col width="8.497478991596639" customWidth="1" min="7" max="7"/>
     <col width="10.1109243697479" customWidth="1" min="8" max="8"/>
-    <col width="9.680672268907562" customWidth="1" min="9" max="9"/>
-    <col width="9.465546218487395" customWidth="1" min="10" max="10"/>
-    <col width="9.465546218487395" customWidth="1" min="11" max="11"/>
-    <col width="8.712605042016806" customWidth="1" min="12" max="12"/>
-    <col width="7.20672268907563" customWidth="1" min="13" max="13"/>
-    <col width="4.840336134453781" customWidth="1" min="14" max="14"/>
+    <col width="9.89579831932773" customWidth="1" min="9" max="9"/>
+    <col width="10.1109243697479" customWidth="1" min="10" max="10"/>
+    <col width="9.680672268907562" customWidth="1" min="11" max="11"/>
+    <col width="9.465546218487395" customWidth="1" min="12" max="12"/>
+    <col width="9.465546218487395" customWidth="1" min="13" max="13"/>
+    <col width="8.712605042016806" customWidth="1" min="14" max="14"/>
+    <col width="7.20672268907563" customWidth="1" min="15" max="15"/>
+    <col width="4.840336134453781" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.75294117647059" customHeight="1">
@@ -795,21 +838,23 @@
           <t>EMPRESA DE FERROCARRILES DEL ESTADO-ZONA SUR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>EQUIPO TRACCIÓN CC</t>
         </is>
       </c>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
       <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="3" t="n"/>
     </row>
     <row r="2" ht="32.75294117647059" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -822,58 +867,68 @@
           <t>SERVICIOS</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>MAQUINISTA AYUDANTE</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>APERTURA TRASLADO</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>MAQUINISTA</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>AYUDANTE</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>APERTURA</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>TRASLADO</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>INICIO SERVICIO</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>TERMINO</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>TERMINO</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>TRASLADO</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>ENTREGA</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>TERMINO</t>
         </is>
       </c>
-      <c r="N2" s="7" t="n"/>
+      <c r="P2" s="12" t="n"/>
     </row>
     <row r="3" ht="24.84705882352942" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -907,50 +962,56 @@
           </r>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>N. OLMOS E. RAMIREZ</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>3:25 1:30</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>N. OLMOS</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>E. RAMIREZ</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>HQ V4-ZW</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="I3" s="19" t="n">
         <v>0.2048611111111111</v>
       </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="n">
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K3" s="19" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="L3" s="19" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="M3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="N3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="12" t="n">
+      <c r="O3" s="21" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="P3" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -965,50 +1026,56 @@
           <t>20000-001-022-023-036</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>L. PEDREROS C. SOTO</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>3:40 1:30</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>L. PEDREROS</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>C. SOTO</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>CW V2-N</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="I4" s="19" t="n">
         <v>0.2152777777777778</v>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="K4" s="19" t="n">
         <v>0.4270833333333333</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="L4" s="19" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="M4" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="N4" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="O4" s="19" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="P4" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1046,50 +1113,56 @@
           </r>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>G. LEIVA D. PROVOSTE</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>3:25 1:30</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>G. LEIVA</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>D. PROVOSTE</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>HQ V4-QU</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="I5" s="19" t="n">
         <v>0.2048611111111111</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n">
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="L5" s="19" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="M5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="N5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="O5" s="21" t="n">
         <v>0.4548611111111111</v>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="P5" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1119,50 +1192,56 @@
           </r>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>D. CASANOVA B. ESPINOZA</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>3:55 1:30</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>D. CASANOVA</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>B. ESPINOZA</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.1631944444444444</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>CW V2-S</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="I6" s="19" t="n">
         <v>0.2256944444444444</v>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>GU V4-C</t>
         </is>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.4131944444444444</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="L6" s="19" t="n">
         <v>0.3923611111111111</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="M6" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="N6" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="O6" s="19" t="n">
         <v>0.4756944444444444</v>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1208,52 +1287,58 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>C. HENRIQUEZ D. GALDAMES</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>16:30 0:00</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>C. HENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>D. GALDAMES</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>EZ V2</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="I7" s="19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>LJ CO</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="K7" s="19" t="n">
         <v>0.9895833333333334</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="L7" s="19" t="n">
         <v>0.96875</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="M7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="N7" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="O7" s="21" t="n">
         <v>0.9895833333333334</v>
       </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>LJ</t>
         </is>
       </c>
     </row>
@@ -1297,50 +1382,56 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>J. CABEZA (+) A. FUENTES</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>5:50 0:00</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>J. CABEZA (+)</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>A. FUENTES</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>LJ CO</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="I8" s="19" t="n">
         <v>0.2430555555555556</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="n">
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="L8" s="19" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="M8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="N8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="O8" s="21" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="P8" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1370,50 +1461,56 @@
           </r>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>N. HENRIQUEZ C. RIOS (+)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>4:00 0:45</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>N. HENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C. RIOS (+)</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>CC V4/CV</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="I9" s="19" t="n">
         <v>0.1979166666666667</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="K9" s="19" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="L9" s="19" t="n">
         <v>0.4340277777777778</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="M9" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="N9" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="O9" s="19" t="n">
         <v>0.4756944444444444</v>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1443,50 +1540,56 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>R. GARRIDO E. TOLEDO</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>4:00 0:45</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>R. GARRIDO</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>E. TOLEDO</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>CC V4/EZ</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="I10" s="19" t="n">
         <v>0.1979166666666667</v>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>CC V8</t>
         </is>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="K10" s="19" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="L10" s="19" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="M10" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="N10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="O10" s="19" t="n">
         <v>0.4756944444444444</v>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="P10" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1496,47 +1599,49 @@
       <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>3:30 0:00</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="n">
+      <c r="G11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="11" t="n">
+      <c r="L11" s="27" t="n"/>
+      <c r="M11" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="11" t="n">
+      <c r="N11" s="27" t="n"/>
+      <c r="O11" s="19" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="P11" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1566,50 +1671,56 @@
           </r>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>E. SUAREZ O. LARENAS</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>4:45 1:30</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>E. SUAREZ</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>O. LARENAS</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.1979166666666667</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>CW V1-N</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="I12" s="19" t="n">
         <v>0.2604166666666667</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n">
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
         <v>0.4895833333333333</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="L12" s="19" t="n">
         <v>0.4895833333333333</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="M12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="N12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="O12" s="19" t="n">
         <v>0.4895833333333333</v>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="P12" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1639,50 +1750,56 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>G. DURAN J. ZAMORA</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>4:30 1:00</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>G. DURAN</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>J. ZAMORA</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>LM V3/ES</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="I13" s="19" t="n">
         <v>0.2291666666666667</v>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="K13" s="19" t="n">
         <v>0.4618055555555556</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="L13" s="19" t="n">
         <v>0.4513888888888889</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="M13" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="N13" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="O13" s="19" t="n">
         <v>0.4930555555555556</v>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="P13" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1728,50 +1845,56 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>H. RIQUELME C. DAZA</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>4:40 1:30</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>H. RIQUELME</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>C. DAZA</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>GU V4-N</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="I14" s="19" t="n">
         <v>0.2569444444444444</v>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n">
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="L14" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="M14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="N14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="O14" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="P14" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1809,50 +1932,56 @@
           </r>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>R. MORA J. MELLA</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>4:15 1:30</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>R. MORA</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>J. MELLA</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.1770833333333333</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>LM V3/CC</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="I15" s="19" t="n">
         <v>0.2395833333333333</v>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>CW V1-S</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="K15" s="19" t="n">
         <v>0.4479166666666667</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="L15" s="19" t="n">
         <v>0.4270833333333333</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="M15" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="N15" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="O15" s="19" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="P15" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1906,50 +2035,56 @@
           </r>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>W. GONZALEZ D. OÑATE</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>4:50 1:30</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>W. GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>D. OÑATE</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.2013888888888889</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>GU V4-C</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="I16" s="19" t="n">
         <v>0.2638888888888889</v>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n">
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="L16" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="M16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="N16" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="O16" s="19" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="P16" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -1987,50 +2122,56 @@
           </r>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>J. MELO (-) D. AVELLO +)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>4:50 1:30</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>J. MELO (-)</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>D. AVELLO (+)</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.2013888888888889</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>GU V4-S</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="I17" s="19" t="n">
         <v>0.2638888888888889</v>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="n">
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="L17" s="19" t="n">
         <v>0.4895833333333333</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="M17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="N17" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="O17" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="P17" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2040,47 +2181,49 @@
       <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>4:00 0:00</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n">
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="n">
+      <c r="G18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="11" t="n">
+      <c r="L18" s="27" t="n"/>
+      <c r="M18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="11" t="n">
+      <c r="N18" s="27" t="n"/>
+      <c r="O18" s="19" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="P18" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2095,58 +2238,64 @@
           <t>20016-017-034-035-048</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>L. ROJAS V. PARRA</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>4:55 1:30</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>L. ROJAS</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>V. PARRA</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0.2048611111111111</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>CW V1-S</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="I19" s="19" t="n">
         <v>0.2673611111111111</v>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="K19" s="19" t="n">
         <v>0.4861111111111111</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="L19" s="19" t="n">
         <v>0.4756944444444444</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="M19" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="N19" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="O19" s="19" t="n">
         <v>0.5173611111111112</v>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="P19" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25.41176470588236" customHeight="1">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2166,18 +2315,20 @@
           </r>
         </is>
       </c>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="20" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="27" t="n"/>
+      <c r="L20" s="27" t="n"/>
+      <c r="M20" s="27" t="n"/>
+      <c r="N20" s="27" t="n"/>
+      <c r="O20" s="27" t="n"/>
+      <c r="P20" s="32" t="n"/>
     </row>
     <row r="21" ht="25.41176470588236" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -2211,58 +2362,64 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>L. CARRIZO D. GARRIDO</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>5:30 0:00</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>L. CARRIZO</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>D. GARRIDO</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>EZ V2</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="I21" s="19" t="n">
         <v>0.2291666666666667</v>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="K21" s="19" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="L21" s="19" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="M21" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="N21" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="O21" s="21" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="P21" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24.84705882352942" customHeight="1">
-      <c r="A22" s="21" t="n"/>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2290,18 +2447,20 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="20" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="27" t="n"/>
+      <c r="I22" s="27" t="n"/>
+      <c r="J22" s="27" t="n"/>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="27" t="n"/>
+      <c r="M22" s="27" t="n"/>
+      <c r="N22" s="27" t="n"/>
+      <c r="O22" s="27" t="n"/>
+      <c r="P22" s="32" t="n"/>
     </row>
     <row r="23" ht="25.97647058823529" customHeight="1">
       <c r="A23" s="5" t="n">
@@ -2335,58 +2494,64 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>L. FERNANDEZ J. BURGOS</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>6:00 0:00</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>L. FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>J. BURGOS</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="I23" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="K23" s="19" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="L23" s="19" t="n">
         <v>0.5520833333333334</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="M23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="N23" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="O23" s="21" t="n">
         <v>0.5625</v>
       </c>
-      <c r="N23" s="8" t="inlineStr">
+      <c r="P23" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25.41176470588236" customHeight="1">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2414,18 +2579,20 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="20" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="34" t="n"/>
+      <c r="H24" s="27" t="n"/>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
+      <c r="P24" s="32" t="n"/>
     </row>
     <row r="25" ht="25.41176470588236" customHeight="1">
       <c r="A25" s="5" t="n">
@@ -2467,50 +2634,56 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>B. GONZALEZ P. NAVARRETE</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>7:30 0:00</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>B. GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>P. NAVARRETE</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="I25" s="19" t="n">
         <v>0.3125</v>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>EZ V2</t>
         </is>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="K25" s="19" t="n">
         <v>0.7048611111111112</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="L25" s="19" t="n">
         <v>0.7048611111111112</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="M25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="N25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="O25" s="21" t="n">
         <v>0.7048611111111112</v>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="P25" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2525,58 +2698,64 @@
           <t>20037-050-051-058</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>S. TORRES (+) J. CHAPARRO</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>9:05 0:45</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>S. TORRES (+)</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>J. CHAPARRO</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0.3784722222222222</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="I26" s="19" t="n">
         <v>0.4097222222222222</v>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="K26" s="19" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="L26" s="19" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="M26" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="N26" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="O26" s="21" t="n">
         <v>0.59375</v>
       </c>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="P26" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25.41176470588236" customHeight="1">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2596,22 +2775,24 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>J. CORTEZ</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-      <c r="M27" s="16" t="n"/>
-      <c r="N27" s="20" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="27" t="n"/>
+      <c r="I27" s="27" t="n"/>
+      <c r="J27" s="27" t="n"/>
+      <c r="K27" s="27" t="n"/>
+      <c r="L27" s="27" t="n"/>
+      <c r="M27" s="27" t="n"/>
+      <c r="N27" s="27" t="n"/>
+      <c r="O27" s="27" t="n"/>
+      <c r="P27" s="32" t="n"/>
     </row>
     <row r="28" ht="24.84705882352942" customHeight="1">
       <c r="A28" s="5" t="n">
@@ -2653,50 +2834,56 @@
           </r>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>G. SOLAR B. NOVOA</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>9:45 0:00</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="n">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>G. SOLAR</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>B. NOVOA</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n">
         <v>0.40625</v>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="G28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="K28" s="19" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="L28" s="19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="M28" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="N28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="11" t="n">
+      <c r="O28" s="19" t="n">
         <v>0.71875</v>
       </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="P28" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2711,78 +2898,90 @@
           <t>20054-055-066</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>G. ZUÑIGA (+) M. RIFO</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>9:20 1:30</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>G. ZUÑIGA (+)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>M. RIFO</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>CW</t>
         </is>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="I29" s="19" t="n">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="K29" s="19" t="n">
         <v>0.65625</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="L29" s="19" t="n">
         <v>0.5520833333333334</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="M29" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="N29" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="O29" s="19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="P29" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24.84705882352942" customHeight="1">
-      <c r="A30" s="17" t="n"/>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>P. MUÑOZ M. RAMOS</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="17" t="n"/>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="17" t="n"/>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>P. MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>M. RAMOS</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="28" t="n"/>
+      <c r="J30" s="28" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="28" t="n"/>
+      <c r="N30" s="28" t="n"/>
+      <c r="O30" s="28" t="n"/>
+      <c r="P30" s="28" t="n"/>
     </row>
     <row r="31" ht="25.97647058823529" customHeight="1">
       <c r="A31" s="5" t="n">
@@ -2808,50 +3007,56 @@
           </r>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>N. GONZALEZ S. PEDREROS</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>13:00 0:00</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="n">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>N. GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>S. PEDREROS</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="n">
+      <c r="G31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="L31" s="19" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="K31" s="11" t="n">
+      <c r="M31" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="N31" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="O31" s="21" t="n">
         <v>0.84375</v>
       </c>
-      <c r="N31" s="8" t="inlineStr">
+      <c r="P31" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2905,50 +3110,56 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>A. ARRIAGADA O. SANZANA</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>11:00 0:00</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>A. ARRIAGADA</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>O. SANZANA</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="I32" s="19" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>EZ V4</t>
         </is>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="K32" s="19" t="n">
         <v>0.9722222222222222</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="L32" s="19" t="n">
         <v>0.9513888888888888</v>
       </c>
-      <c r="K32" s="11" t="n">
+      <c r="M32" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="N32" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="O32" s="21" t="n">
         <v>0.9722222222222222</v>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="P32" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -2963,50 +3174,56 @@
           <t>20059-064-065-072-073-090</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>M. VALLEJOS D. CONTRERAS (+)</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>12:15 0:45</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>M. VALLEJOS</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>D. CONTRERAS (+)</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="I33" s="19" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I33" s="11" t="n">
+      <c r="K33" s="19" t="n">
         <v>0.7847222222222222</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="L33" s="19" t="n">
         <v>0.7743055555555556</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="M33" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="N33" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="O33" s="19" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="P33" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3021,53 +3238,59 @@
           <t>20049-056</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>E. CONTRERAS B. TOLEDO</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>10:30 0:45</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>E. CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="inlineStr">
+        <is>
+          <t>B. TOLEDO</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="I34" s="19" t="n">
         <v>0.46875</v>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="K34" s="19" t="n">
         <v>0.5520833333333334</v>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="11" t="n">
+      <c r="L34" s="27" t="n"/>
+      <c r="M34" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L34" s="16" t="n"/>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="27" t="n"/>
+      <c r="O34" s="21" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="N34" s="8" t="inlineStr">
+      <c r="P34" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25.97647058823529" customHeight="1">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="44" t="n">
         <v>28</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3075,58 +3298,64 @@
           <t>057-062-063-068</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>E. CONTRERAS B. TOLEDO</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>12:00 0:45</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>E. CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D35" s="37" t="inlineStr">
+        <is>
+          <t>B. TOLEDO</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="I35" s="19" t="n">
         <v>0.53125</v>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="K35" s="19" t="n">
         <v>0.6909722222222222</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="L35" s="19" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="M35" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="N35" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="O35" s="19" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="N35" s="8" t="inlineStr">
+      <c r="P35" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24.84705882352942" customHeight="1">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3146,68 +3375,72 @@
           </r>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>D. SAAVEDRA</t>
         </is>
       </c>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="20" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
+      <c r="J36" s="27" t="n"/>
+      <c r="K36" s="27" t="n"/>
+      <c r="L36" s="27" t="n"/>
+      <c r="M36" s="27" t="n"/>
+      <c r="N36" s="27" t="n"/>
+      <c r="O36" s="27" t="n"/>
+      <c r="P36" s="32" t="n"/>
     </row>
     <row r="37" ht="25.41176470588236" customHeight="1">
       <c r="A37" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>jornada</t>
         </is>
       </c>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="n">
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="26" t="n"/>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="n">
         <v>0.6875</v>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="34" t="n"/>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="n">
+      <c r="J37" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="L37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="M37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="16" t="n"/>
-      <c r="M37" s="11" t="n">
+      <c r="N37" s="27" t="n"/>
+      <c r="O37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="8" t="inlineStr">
+      <c r="P37" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3245,50 +3478,56 @@
           </r>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>C. ALVEAR A. QUEIROLO</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>14:45 1:30</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>C. ALVEAR</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>A. QUEIROLO</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>GU V4-S</t>
         </is>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="I38" s="19" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>GU V4-S</t>
         </is>
       </c>
-      <c r="I38" s="11" t="n">
+      <c r="K38" s="19" t="n">
         <v>0.8715277777777778</v>
       </c>
-      <c r="J38" s="11" t="n">
+      <c r="L38" s="19" t="n">
         <v>0.8506944444444444</v>
       </c>
-      <c r="K38" s="11" t="n">
+      <c r="M38" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L38" s="11" t="n">
+      <c r="N38" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="O38" s="21" t="n">
         <v>0.9340277777777778</v>
       </c>
-      <c r="N38" s="8" t="inlineStr">
+      <c r="P38" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3298,47 +3537,49 @@
       <c r="A39" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>jornada</t>
         </is>
       </c>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="n">
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="n">
         <v>0.6875</v>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="34" t="n"/>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="n">
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="L39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="M39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="16" t="n"/>
-      <c r="M39" s="11" t="n">
+      <c r="N39" s="27" t="n"/>
+      <c r="O39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="8" t="inlineStr">
+      <c r="P39" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3353,50 +3594,56 @@
           <t>20067-078-079-098-099-114</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>F. PAVEZ** M. ROJAS</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>14:30 0:45</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>F. PAVEZ**</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>M. ROJAS</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="I40" s="19" t="n">
         <v>0.6354166666666666</v>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="J40" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="K40" s="19" t="n">
         <v>0.8854166666666666</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="L40" s="19" t="n">
         <v>0.875</v>
       </c>
-      <c r="K40" s="11" t="n">
+      <c r="M40" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="N40" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M40" s="26" t="n">
+      <c r="O40" s="45" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="N40" s="8" t="inlineStr">
+      <c r="P40" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3450,57 +3697,63 @@
           </r>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>A. SAAVEDRA M. CHANDIA</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>15:45 0:00</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="n">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>A. SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>M. CHANDIA</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="n">
         <v>0.65625</v>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="G41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I41" s="11" t="n">
+      <c r="K41" s="19" t="n">
         <v>0.9340277777777778</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="L41" s="19" t="n">
         <v>0.9340277777777778</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="M41" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="N41" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="11" t="n">
+      <c r="O41" s="19" t="n">
         <v>0.9652777777777778</v>
       </c>
-      <c r="N41" s="8" t="inlineStr">
+      <c r="P41" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24.28235294117647" customHeight="1">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="15" t="n">
         <v>34</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -3508,57 +3761,63 @@
           <t>JORNADA-20107-120-121</t>
         </is>
       </c>
-      <c r="C42" s="27" t="inlineStr">
-        <is>
-          <t>J. TAPIA S. PEÑA (+)</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>16:45 0:45</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>J. TAPIA</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>S. PEÑA (+)</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="I42" s="19" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="J42" s="22" t="inlineStr">
         <is>
           <t>CW V1-S</t>
         </is>
       </c>
-      <c r="I42" s="11" t="n">
+      <c r="K42" s="19" t="n">
         <v>0.9479166666666666</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="L42" s="19" t="n">
         <v>0.9270833333333334</v>
       </c>
-      <c r="K42" s="11" t="n">
+      <c r="M42" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="N42" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="O42" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="N42" s="8" t="inlineStr">
+      <c r="P42" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25.97647058823529" customHeight="1">
-      <c r="A43" s="25" t="n">
+      <c r="A43" s="44" t="n">
         <v>35</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -3581,50 +3840,56 @@
           </r>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>V. MORALES C. VILLAR</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>17:35 0:45</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>V. MORALES</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>C. VILLAR</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="I43" s="19" t="n">
         <v>0.7638888888888888</v>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="J43" s="22" t="inlineStr">
         <is>
           <t>CW V1-N</t>
         </is>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="K43" s="19" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="L43" s="19" t="n">
         <v>0.9375</v>
       </c>
-      <c r="K43" s="11" t="n">
+      <c r="M43" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="N43" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="O43" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="P43" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3662,50 +3927,56 @@
           </r>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>W. SOLIS M. HUIRCAN</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>18:05 0:00</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="n">
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>W. SOLIS</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>M. HUIRCAN</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="G44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
         <is>
           <t>CW V2-S</t>
         </is>
       </c>
-      <c r="I44" s="11" t="n">
+      <c r="K44" s="19" t="n">
         <v>0.003472222222222222</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="L44" s="19" t="n">
         <v>0.9826388888888888</v>
       </c>
-      <c r="K44" s="11" t="n">
+      <c r="M44" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="N44" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M44" s="11" t="n">
+      <c r="O44" s="19" t="n">
         <v>0.06597222222222222</v>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="P44" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3720,58 +3991,64 @@
           <t>20115-128-129</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
-        <is>
-          <t>F. PAVEZ** C. BRAVO</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>18:05 0:45</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>F. PAVEZ**</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>C. BRAVO</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="I45" s="19" t="n">
         <v>0.7847222222222222</v>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="J45" s="22" t="inlineStr">
         <is>
           <t>CW V2-S</t>
         </is>
       </c>
-      <c r="I45" s="11" t="n">
+      <c r="K45" s="19" t="n">
         <v>0.003472222222222222</v>
       </c>
-      <c r="J45" s="11" t="n">
+      <c r="L45" s="19" t="n">
         <v>0.9826388888888888</v>
       </c>
-      <c r="K45" s="11" t="n">
+      <c r="M45" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L45" s="11" t="n">
+      <c r="N45" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M45" s="11" t="n">
+      <c r="O45" s="19" t="n">
         <v>0.06597222222222222</v>
       </c>
-      <c r="N45" s="8" t="inlineStr">
+      <c r="P45" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24.84705882352942" customHeight="1">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="A46" s="28" t="n"/>
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3791,18 +4068,20 @@
           </r>
         </is>
       </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="16" t="n"/>
-      <c r="J46" s="16" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="16" t="n"/>
-      <c r="M46" s="16" t="n"/>
-      <c r="N46" s="20" t="n"/>
+      <c r="C46" s="30" t="n"/>
+      <c r="D46" s="31" t="n"/>
+      <c r="E46" s="32" t="n"/>
+      <c r="F46" s="33" t="n"/>
+      <c r="G46" s="34" t="n"/>
+      <c r="H46" s="27" t="n"/>
+      <c r="I46" s="27" t="n"/>
+      <c r="J46" s="27" t="n"/>
+      <c r="K46" s="27" t="n"/>
+      <c r="L46" s="27" t="n"/>
+      <c r="M46" s="27" t="n"/>
+      <c r="N46" s="27" t="n"/>
+      <c r="O46" s="27" t="n"/>
+      <c r="P46" s="32" t="n"/>
     </row>
     <row r="47" ht="25.97647058823529" customHeight="1">
       <c r="A47" s="5" t="n">
@@ -3836,50 +4115,56 @@
           </r>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>R. PRADENAS M. PEREIRA</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>16:00 0:00</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>R. PRADENAS</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>M. PEREIRA</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>EZ V1</t>
         </is>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="I47" s="19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>LM V3/CC</t>
         </is>
       </c>
-      <c r="I47" s="11" t="n">
+      <c r="K47" s="19" t="n">
         <v>0.9236111111111112</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="L47" s="19" t="n">
         <v>0.9027777777777778</v>
       </c>
-      <c r="K47" s="11" t="n">
+      <c r="M47" s="19" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="L47" s="11" t="n">
+      <c r="N47" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="O47" s="21" t="n">
         <v>0.9652777777777778</v>
       </c>
-      <c r="N47" s="8" t="inlineStr">
+      <c r="P47" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3917,50 +4202,56 @@
           </r>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>J. HERRERA L. MONTALBA</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>16:00 0:00</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>J. HERRERA</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>L. MONTALBA</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>EZ V1</t>
         </is>
       </c>
-      <c r="G48" s="11" t="n">
+      <c r="I48" s="19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="J48" s="22" t="inlineStr">
         <is>
           <t>GU V4-C</t>
         </is>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="K48" s="19" t="n">
         <v>0.8506944444444444</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="L48" s="19" t="n">
         <v>0.8298611111111112</v>
       </c>
-      <c r="K48" s="11" t="n">
+      <c r="M48" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L48" s="11" t="n">
+      <c r="N48" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M48" s="12" t="n">
+      <c r="O48" s="21" t="n">
         <v>0.9131944444444444</v>
       </c>
-      <c r="N48" s="8" t="inlineStr">
+      <c r="P48" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -3970,48 +4261,50 @@
       <c r="A49" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>jornada</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="n">
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="n">
+      <c r="G49" s="34" t="n"/>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I49" s="16" t="n"/>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="16" t="n"/>
-      <c r="M49" s="26" t="n">
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K49" s="27" t="n"/>
+      <c r="L49" s="27" t="n"/>
+      <c r="M49" s="27" t="n"/>
+      <c r="N49" s="27" t="n"/>
+      <c r="O49" s="45" t="n">
         <v>0.8541666666666666</v>
       </c>
-      <c r="N49" s="8" t="inlineStr">
+      <c r="P49" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24.84705882352942" customHeight="1">
-      <c r="A50" s="25" t="n">
+      <c r="A50" s="44" t="n">
         <v>41</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4034,50 +4327,56 @@
           </r>
         </is>
       </c>
-      <c r="C50" s="22" t="inlineStr">
-        <is>
-          <t>C. BUSTAMANTE** M. NAVARRETE</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>16:30 0:45</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>C. BUSTAMANTE**</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>M. NAVARRETE</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="G50" s="11" t="n">
+      <c r="I50" s="19" t="n">
         <v>0.71875</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="J50" s="18" t="inlineStr">
         <is>
           <t>LM V3/ES</t>
         </is>
       </c>
-      <c r="I50" s="11" t="n">
+      <c r="K50" s="19" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="L50" s="19" t="n">
         <v>0.9375</v>
       </c>
-      <c r="K50" s="11" t="n">
+      <c r="M50" s="19" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="L50" s="11" t="n">
+      <c r="N50" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M50" s="11" t="n">
+      <c r="O50" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="P50" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -4107,55 +4406,61 @@
           </r>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>A. ASTETE A. PARRA</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>17:00 0:00</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>A. ASTETE</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>A. PARRA</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>EZ V2</t>
         </is>
       </c>
-      <c r="G51" s="11" t="n">
+      <c r="I51" s="19" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="I51" s="11" t="n">
+      <c r="K51" s="19" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="J51" s="16" t="n"/>
-      <c r="K51" s="11" t="n">
+      <c r="L51" s="27" t="n"/>
+      <c r="M51" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L51" s="11" t="n">
+      <c r="N51" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="O51" s="21" t="n">
         <v>0.9479166666666666</v>
       </c>
-      <c r="N51" s="8" t="inlineStr">
+      <c r="P51" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24.84705882352942" customHeight="1">
-      <c r="A52" s="8" t="n">
+      <c r="A52" s="15" t="n">
         <v>43</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4163,50 +4468,56 @@
           <t>20071-088-089-106</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>N. J. HENRIQUEZ B. ROCHA</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>15:10 0:45</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>N. J. HENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>B. ROCHA</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>0.6319444444444444</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>CC V8</t>
         </is>
       </c>
-      <c r="G52" s="11" t="n">
+      <c r="I52" s="19" t="n">
         <v>0.6631944444444444</v>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I52" s="11" t="n">
+      <c r="K52" s="19" t="n">
         <v>0.84375</v>
       </c>
-      <c r="J52" s="11" t="n">
+      <c r="L52" s="19" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="K52" s="11" t="n">
+      <c r="M52" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L52" s="11" t="n">
+      <c r="N52" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M52" s="12" t="n">
+      <c r="O52" s="21" t="n">
         <v>0.875</v>
       </c>
-      <c r="N52" s="8" t="inlineStr">
+      <c r="P52" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -4236,58 +4547,64 @@
           </r>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>M. CONTRERAS C. BIZAMA</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>15:15 0:00</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>M. CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>C. BIZAMA</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>EZ V2</t>
         </is>
       </c>
-      <c r="G53" s="11" t="n">
+      <c r="I53" s="19" t="n">
         <v>0.6354166666666666</v>
       </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="n">
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="n">
         <v>0.9375</v>
       </c>
-      <c r="J53" s="11" t="n">
+      <c r="L53" s="19" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="K53" s="11" t="n">
+      <c r="M53" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="11" t="n">
+      <c r="N53" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M53" s="26" t="n">
+      <c r="O53" s="45" t="n">
         <v>0.9375</v>
       </c>
-      <c r="N53" s="8" t="inlineStr">
+      <c r="P53" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25.41176470588236" customHeight="1">
-      <c r="A54" s="21" t="n"/>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="A54" s="35" t="n"/>
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4307,25 +4624,27 @@
           </r>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>E. ROMAN</t>
         </is>
       </c>
-      <c r="D54" s="20" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n"/>
-      <c r="M54" s="16" t="n"/>
-      <c r="N54" s="20" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="33" t="n"/>
+      <c r="G54" s="34" t="n"/>
+      <c r="H54" s="27" t="n"/>
+      <c r="I54" s="27" t="n"/>
+      <c r="J54" s="27" t="n"/>
+      <c r="K54" s="27" t="n"/>
+      <c r="L54" s="27" t="n"/>
+      <c r="M54" s="27" t="n"/>
+      <c r="N54" s="27" t="n"/>
+      <c r="O54" s="27" t="n"/>
+      <c r="P54" s="32" t="n"/>
     </row>
     <row r="55" ht="25.41176470588236" customHeight="1">
-      <c r="A55" s="25" t="n">
+      <c r="A55" s="44" t="n">
         <v>45</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -4333,50 +4652,56 @@
           <t>20069-084-085-104</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>C. BUSTAMANTE** M. SANHUEZA (+)</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>15:20 0:45</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>C. BUSTAMANTE**</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>M. SANHUEZA (+)</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="G55" s="11" t="n">
+      <c r="I55" s="19" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="I55" s="11" t="n">
+      <c r="K55" s="19" t="n">
         <v>0.8298611111111112</v>
       </c>
-      <c r="J55" s="11" t="n">
+      <c r="L55" s="19" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="K55" s="11" t="n">
+      <c r="M55" s="19" t="n">
         <v>0.03125</v>
       </c>
-      <c r="L55" s="11" t="n">
+      <c r="N55" s="19" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="M55" s="26" t="n">
+      <c r="O55" s="45" t="n">
         <v>0.8611111111111112</v>
       </c>
-      <c r="N55" s="8" t="inlineStr">
+      <c r="P55" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -4414,50 +4739,56 @@
           </r>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>P. DONOSO C. CUEVAS</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>14:50 1:30</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>P. DONOSO</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>C. CUEVAS</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="n">
+        <v>0.6180555555555556</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
         <is>
           <t>GU V4-C</t>
         </is>
       </c>
-      <c r="G56" s="11" t="n">
+      <c r="I56" s="19" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="J56" s="22" t="inlineStr">
         <is>
           <t>GU V4-N</t>
         </is>
       </c>
-      <c r="I56" s="11" t="n">
+      <c r="K56" s="19" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="J56" s="11" t="n">
+      <c r="L56" s="19" t="n">
         <v>0.7986111111111112</v>
       </c>
-      <c r="K56" s="11" t="n">
+      <c r="M56" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L56" s="11" t="n">
+      <c r="N56" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M56" s="11" t="n">
+      <c r="O56" s="19" t="n">
         <v>0.8819444444444444</v>
       </c>
-      <c r="N56" s="8" t="inlineStr">
+      <c r="P56" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -4487,50 +4818,56 @@
           </r>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>S. YAÑEZ (+) O. HENRIQUEZ</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>9:30 0:45</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>S. YAÑEZ (+)</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>O. HENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>CC V4</t>
         </is>
       </c>
-      <c r="G57" s="11" t="n">
+      <c r="I57" s="19" t="n">
         <v>0.4270833333333333</v>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="J57" s="22" t="inlineStr">
         <is>
           <t>GU V4-S</t>
         </is>
       </c>
-      <c r="I57" s="11" t="n">
+      <c r="K57" s="19" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J57" s="11" t="n">
+      <c r="L57" s="19" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="K57" s="11" t="n">
+      <c r="M57" s="19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="L57" s="11" t="n">
+      <c r="N57" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M57" s="26" t="n">
+      <c r="O57" s="45" t="n">
         <v>0.625</v>
       </c>
-      <c r="N57" s="8" t="inlineStr">
+      <c r="P57" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
@@ -4540,85 +4877,95 @@
       <c r="A58" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
-        <is>
-          <t>C. PUENTES B. ANGEL</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="17" t="n"/>
-      <c r="G58" s="17" t="n"/>
-      <c r="H58" s="17" t="n"/>
-      <c r="I58" s="17" t="n"/>
-      <c r="J58" s="17" t="n"/>
-      <c r="K58" s="17" t="n"/>
-      <c r="L58" s="17" t="n"/>
-      <c r="M58" s="17" t="n"/>
-      <c r="N58" s="17" t="n"/>
+      <c r="C58" s="40" t="inlineStr">
+        <is>
+          <t>C. PUENTES</t>
+        </is>
+      </c>
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>B. ANGEL</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="n"/>
+      <c r="F58" s="42" t="n"/>
+      <c r="G58" s="43" t="n"/>
+      <c r="H58" s="28" t="n"/>
+      <c r="I58" s="28" t="n"/>
+      <c r="J58" s="28" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="28" t="n"/>
+      <c r="M58" s="28" t="n"/>
+      <c r="N58" s="28" t="n"/>
+      <c r="O58" s="28" t="n"/>
+      <c r="P58" s="28" t="n"/>
     </row>
     <row r="59" ht="25.41176470588236" customHeight="1">
-      <c r="A59" s="17" t="n"/>
+      <c r="A59" s="28" t="n"/>
       <c r="B59" s="5" t="inlineStr">
         <is>
           <t>REC VALLE</t>
         </is>
       </c>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>EZ</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="n">
+      <c r="C59" s="42" t="n"/>
+      <c r="D59" s="43" t="n"/>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>EZ</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="n">
         <v>0.375</v>
       </c>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="11" t="n">
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="27" t="n"/>
+      <c r="I59" s="19" t="n">
         <v>0.375</v>
       </c>
-      <c r="H59" s="16" t="n"/>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
-      <c r="M59" s="11" t="n">
+      <c r="J59" s="27" t="n"/>
+      <c r="K59" s="27" t="n"/>
+      <c r="L59" s="27" t="n"/>
+      <c r="M59" s="27" t="n"/>
+      <c r="N59" s="27" t="n"/>
+      <c r="O59" s="19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="N59" s="8" t="inlineStr">
+      <c r="P59" s="15" t="inlineStr">
         <is>
           <t>EZ</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25.41176470588236" customHeight="1">
-      <c r="A60" s="17" t="n"/>
+      <c r="A60" s="28" t="n"/>
       <c r="B60" s="5" t="inlineStr">
         <is>
           <t>SIMULADORES 08:30 A 14:30 HORAS</t>
         </is>
       </c>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="17" t="n"/>
+      <c r="C60" s="47" t="n"/>
+      <c r="D60" s="3" t="n"/>
       <c r="E60" s="28" t="n"/>
-      <c r="F60" s="28" t="n"/>
-      <c r="G60" s="28" t="n"/>
-      <c r="H60" s="28" t="n"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="28" t="n"/>
-      <c r="K60" s="28" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="28" t="n"/>
-      <c r="N60" s="7" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="12" t="n"/>
     </row>
     <row r="61" ht="24.84705882352942" customHeight="1">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="A61" s="28" t="n"/>
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4643,21 +4990,23 @@
           <t>D. CASTILLO</t>
         </is>
       </c>
-      <c r="D61" s="17" t="n"/>
+      <c r="D61" s="12" t="n"/>
       <c r="E61" s="28" t="n"/>
-      <c r="F61" s="28" t="n"/>
-      <c r="G61" s="28" t="n"/>
-      <c r="H61" s="28" t="n"/>
-      <c r="I61" s="28" t="n"/>
-      <c r="J61" s="28" t="n"/>
-      <c r="K61" s="28" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="28" t="n"/>
-      <c r="N61" s="7" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="12" t="n"/>
     </row>
     <row r="62" ht="25.97647058823529" customHeight="1">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="A62" s="28" t="n"/>
+      <c r="B62" s="48" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4697,388 +5046,457 @@
           </r>
         </is>
       </c>
-      <c r="D62" s="17" t="n"/>
+      <c r="D62" s="12" t="n"/>
       <c r="E62" s="28" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="28" t="n"/>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="28" t="n"/>
-      <c r="J62" s="28" t="n"/>
-      <c r="K62" s="28" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="28" t="n"/>
-      <c r="N62" s="7" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="12" t="n"/>
     </row>
     <row r="63" ht="25.41176470588236" customHeight="1">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="30" t="inlineStr">
+      <c r="A63" s="28" t="n"/>
+      <c r="B63" s="49" t="inlineStr">
         <is>
           <t>BAJADA NUEVOS PROCEDIMIENTOS EN EZ DE 10:00 A 12:00 HORAS</t>
         </is>
       </c>
-      <c r="C63" s="31" t="inlineStr">
+      <c r="C63" s="50" t="inlineStr">
         <is>
           <t>C. ARREPOL</t>
         </is>
       </c>
-      <c r="D63" s="17" t="n"/>
+      <c r="D63" s="12" t="n"/>
       <c r="E63" s="28" t="n"/>
-      <c r="F63" s="28" t="n"/>
-      <c r="G63" s="28" t="n"/>
-      <c r="H63" s="28" t="n"/>
-      <c r="I63" s="28" t="n"/>
-      <c r="J63" s="28" t="n"/>
-      <c r="K63" s="28" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="28" t="n"/>
-      <c r="N63" s="7" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="12" t="n"/>
     </row>
     <row r="64" ht="25.41176470588236" customHeight="1">
-      <c r="A64" s="17" t="n"/>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="A64" s="28" t="n"/>
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>N. OLMOS</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>E. RAMIREZ H. RIQUELME</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n"/>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>E. RAMIREZ</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>H. RIQUELME</t>
+        </is>
+      </c>
       <c r="E64" s="28" t="n"/>
-      <c r="F64" s="28" t="n"/>
-      <c r="G64" s="28" t="n"/>
-      <c r="H64" s="28" t="n"/>
-      <c r="I64" s="28" t="n"/>
-      <c r="J64" s="28" t="n"/>
-      <c r="K64" s="28" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="28" t="n"/>
-      <c r="N64" s="7" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="12" t="n"/>
     </row>
     <row r="65" ht="25.41176470588236" customHeight="1">
-      <c r="A65" s="17" t="n"/>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="A65" s="28" t="n"/>
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>G. LEIVA</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>D. PROVOSTE C. DAZA</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="n"/>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>D. PROVOSTE</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>C. DAZA</t>
+        </is>
+      </c>
       <c r="E65" s="28" t="n"/>
-      <c r="F65" s="28" t="n"/>
-      <c r="G65" s="28" t="n"/>
-      <c r="H65" s="28" t="n"/>
-      <c r="I65" s="28" t="n"/>
-      <c r="J65" s="28" t="n"/>
-      <c r="K65" s="28" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="28" t="n"/>
-      <c r="N65" s="7" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="12" t="n"/>
     </row>
     <row r="66" ht="25.41176470588236" customHeight="1">
-      <c r="A66" s="17" t="n"/>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="A66" s="28" t="n"/>
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>J. CABEZA (+)</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>A. FUENTES W. GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="n"/>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>A. FUENTES</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>W. GONZALEZ</t>
+        </is>
+      </c>
       <c r="E66" s="28" t="n"/>
-      <c r="F66" s="28" t="n"/>
-      <c r="G66" s="28" t="n"/>
-      <c r="H66" s="28" t="n"/>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="28" t="n"/>
-      <c r="K66" s="28" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="28" t="n"/>
-      <c r="N66" s="7" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="12" t="n"/>
     </row>
     <row r="67" ht="24.84705882352942" customHeight="1">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="A67" s="28" t="n"/>
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>G. DURAN</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>J. ZAMORA D. OÑATE</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="n"/>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>J. ZAMORA</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>D. OÑATE</t>
+        </is>
+      </c>
       <c r="E67" s="28" t="n"/>
-      <c r="F67" s="28" t="n"/>
-      <c r="G67" s="28" t="n"/>
-      <c r="H67" s="28" t="n"/>
-      <c r="I67" s="28" t="n"/>
-      <c r="J67" s="28" t="n"/>
-      <c r="K67" s="28" t="n"/>
-      <c r="L67" s="28" t="n"/>
-      <c r="M67" s="28" t="n"/>
-      <c r="N67" s="7" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="12" t="n"/>
     </row>
     <row r="68" ht="25.97647058823529" customHeight="1">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="A68" s="28" t="n"/>
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>J. MELO (-)</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>D. AVELLO (+)</t>
         </is>
       </c>
-      <c r="D68" s="17" t="n"/>
+      <c r="D68" s="51" t="n"/>
       <c r="E68" s="28" t="n"/>
-      <c r="F68" s="28" t="n"/>
-      <c r="G68" s="28" t="n"/>
-      <c r="H68" s="28" t="n"/>
-      <c r="I68" s="28" t="n"/>
-      <c r="J68" s="28" t="n"/>
-      <c r="K68" s="28" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="28" t="n"/>
-      <c r="N68" s="7" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="12" t="n"/>
     </row>
     <row r="69" ht="18.07058823529412" customHeight="1">
-      <c r="A69" s="17" t="n"/>
+      <c r="A69" s="28" t="n"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
           <t>LICENCIA MEDICA</t>
         </is>
       </c>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="32" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="28" t="n"/>
-      <c r="G69" s="28" t="n"/>
-      <c r="H69" s="28" t="n"/>
-      <c r="I69" s="28" t="n"/>
-      <c r="J69" s="28" t="n"/>
-      <c r="K69" s="28" t="n"/>
-      <c r="L69" s="28" t="n"/>
-      <c r="M69" s="28" t="n"/>
-      <c r="N69" s="7" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="52" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="12" t="n"/>
     </row>
     <row r="70" ht="18.07058823529412" customHeight="1">
-      <c r="A70" s="17" t="n"/>
+      <c r="A70" s="28" t="n"/>
       <c r="B70" s="5" t="inlineStr">
         <is>
           <t>A. ASCENCIO</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>J. ARANEDA P. REYES</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="n"/>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>J. ARANEDA</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>P. REYES</t>
+        </is>
+      </c>
       <c r="E70" s="28" t="n"/>
-      <c r="F70" s="28" t="n"/>
-      <c r="G70" s="28" t="n"/>
-      <c r="H70" s="28" t="n"/>
-      <c r="I70" s="28" t="n"/>
-      <c r="J70" s="28" t="n"/>
-      <c r="K70" s="28" t="n"/>
-      <c r="L70" s="28" t="n"/>
-      <c r="M70" s="28" t="n"/>
-      <c r="N70" s="7" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="12" t="n"/>
     </row>
     <row r="71" ht="18.07058823529412" customHeight="1">
-      <c r="A71" s="17" t="n"/>
+      <c r="A71" s="28" t="n"/>
       <c r="B71" s="5" t="inlineStr">
         <is>
           <t>B. HENRIQUEZ</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>C. PILAR G. ARANDA</t>
-        </is>
-      </c>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="34" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>C. PILAR</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>G. ARANDA</t>
+        </is>
+      </c>
+      <c r="E71" s="53" t="n"/>
+      <c r="F71" s="54" t="inlineStr">
         <is>
           <t>ITINERARIO VIGENTE N° 2-448, a contar del 22-06-2026.</t>
         </is>
       </c>
-      <c r="F71" s="35" t="n"/>
-      <c r="G71" s="35" t="n"/>
-      <c r="H71" s="35" t="n"/>
-      <c r="I71" s="35" t="n"/>
-      <c r="J71" s="35" t="n"/>
-      <c r="K71" s="35" t="n"/>
-      <c r="L71" s="35" t="n"/>
-      <c r="M71" s="36" t="n"/>
-      <c r="N71" s="33" t="n"/>
+      <c r="G71" s="55" t="n"/>
+      <c r="H71" s="55" t="n"/>
+      <c r="I71" s="55" t="n"/>
+      <c r="J71" s="55" t="n"/>
+      <c r="K71" s="55" t="n"/>
+      <c r="L71" s="55" t="n"/>
+      <c r="M71" s="55" t="n"/>
+      <c r="N71" s="55" t="n"/>
+      <c r="O71" s="56" t="n"/>
+      <c r="P71" s="53" t="n"/>
     </row>
     <row r="72" ht="18.07058823529412" customHeight="1">
-      <c r="A72" s="17" t="n"/>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="A72" s="28" t="n"/>
+      <c r="B72" s="24" t="inlineStr">
         <is>
           <t>I. BURGOS PILAR</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>C. BELLO L. PEREZ</t>
-        </is>
-      </c>
-      <c r="D72" s="37" t="n"/>
-      <c r="E72" s="38" t="n"/>
-      <c r="M72" s="39" t="n"/>
-      <c r="N72" s="37" t="n"/>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>C. BELLO</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>L. PEREZ</t>
+        </is>
+      </c>
+      <c r="E72" s="57" t="n"/>
+      <c r="F72" s="58" t="n"/>
+      <c r="O72" s="59" t="n"/>
+      <c r="P72" s="57" t="n"/>
     </row>
     <row r="73" ht="18.07058823529412" customHeight="1">
-      <c r="A73" s="17" t="n"/>
+      <c r="A73" s="28" t="n"/>
       <c r="B73" s="5" t="inlineStr">
         <is>
           <t>B. BUSTAMANTE</t>
         </is>
       </c>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="37" t="n"/>
-      <c r="E73" s="38" t="n"/>
-      <c r="M73" s="39" t="n"/>
-      <c r="N73" s="37" t="n"/>
+      <c r="C73" s="42" t="n"/>
+      <c r="D73" s="43" t="n"/>
+      <c r="E73" s="57" t="n"/>
+      <c r="F73" s="58" t="n"/>
+      <c r="O73" s="59" t="n"/>
+      <c r="P73" s="57" t="n"/>
     </row>
     <row r="74" ht="18.07058823529412" customHeight="1">
-      <c r="A74" s="17" t="n"/>
+      <c r="A74" s="28" t="n"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
           <t>FERIADO</t>
         </is>
       </c>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="37" t="n"/>
-      <c r="E74" s="40" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="57" t="n"/>
+      <c r="F74" s="47" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="37" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="57" t="n"/>
     </row>
     <row r="75" ht="18.07058823529412" customHeight="1">
-      <c r="A75" s="17" t="n"/>
-      <c r="B75" s="41" t="inlineStr">
+      <c r="A75" s="28" t="n"/>
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>J. MONTIEL</t>
         </is>
       </c>
-      <c r="C75" s="42" t="inlineStr">
+      <c r="C75" s="60" t="inlineStr">
         <is>
           <t>C. ACUÑA</t>
         </is>
       </c>
-      <c r="D75" s="17" t="n"/>
-      <c r="E75" s="35" t="n"/>
-      <c r="F75" s="35" t="n"/>
-      <c r="G75" s="35" t="n"/>
-      <c r="H75" s="35" t="n"/>
-      <c r="I75" s="35" t="n"/>
-      <c r="J75" s="35" t="n"/>
-      <c r="K75" s="35" t="n"/>
-      <c r="L75" s="35" t="n"/>
-      <c r="M75" s="35" t="n"/>
-      <c r="N75" s="36" t="n"/>
+      <c r="D75" s="43" t="n"/>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="55" t="n"/>
+      <c r="G75" s="55" t="n"/>
+      <c r="H75" s="55" t="n"/>
+      <c r="I75" s="55" t="n"/>
+      <c r="J75" s="55" t="n"/>
+      <c r="K75" s="55" t="n"/>
+      <c r="L75" s="55" t="n"/>
+      <c r="M75" s="55" t="n"/>
+      <c r="N75" s="55" t="n"/>
+      <c r="O75" s="55" t="n"/>
+      <c r="P75" s="56" t="n"/>
     </row>
     <row r="76" ht="18.07058823529412" customHeight="1">
-      <c r="A76" s="17" t="n"/>
+      <c r="A76" s="28" t="n"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
           <t>PERMISO ESPECIAL</t>
         </is>
       </c>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="38" t="n"/>
-      <c r="N76" s="39" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="58" t="n"/>
+      <c r="P76" s="59" t="n"/>
     </row>
     <row r="77" ht="18.63529411764706" customHeight="1">
-      <c r="A77" s="17" t="n"/>
-      <c r="B77" s="41" t="inlineStr">
+      <c r="A77" s="28" t="n"/>
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>R. GUTIERREZ</t>
         </is>
       </c>
-      <c r="C77" s="42" t="inlineStr">
-        <is>
-          <t>M. ARRIAGADA B. MOLINA</t>
-        </is>
-      </c>
-      <c r="D77" s="40" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
+      <c r="C77" s="60" t="inlineStr">
+        <is>
+          <t>M. ARRIAGADA</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>B. MOLINA</t>
+        </is>
+      </c>
+      <c r="E77" s="47" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="3" t="n"/>
     </row>
     <row r="78" ht="15.81176470588235" customHeight="1">
-      <c r="A78" s="32" t="n"/>
-      <c r="B78" s="32" t="n"/>
-      <c r="C78" s="7" t="n"/>
-      <c r="D78" s="32" t="n"/>
-      <c r="E78" s="32" t="n"/>
-      <c r="F78" s="32" t="n"/>
-      <c r="G78" s="32" t="n"/>
-      <c r="H78" s="32" t="n"/>
-      <c r="I78" s="28" t="n"/>
-      <c r="J78" s="28" t="n"/>
-      <c r="K78" s="28" t="n"/>
-      <c r="L78" s="7" t="n"/>
-      <c r="M78" s="32" t="n"/>
-      <c r="N78" s="7" t="n"/>
+      <c r="A78" s="52" t="n"/>
+      <c r="B78" s="52" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="52" t="n"/>
+      <c r="F78" s="61" t="n"/>
+      <c r="G78" s="62" t="n"/>
+      <c r="H78" s="52" t="n"/>
+      <c r="I78" s="52" t="n"/>
+      <c r="J78" s="61" t="n"/>
+      <c r="K78" s="63" t="n"/>
+      <c r="L78" s="63" t="n"/>
+      <c r="M78" s="63" t="n"/>
+      <c r="N78" s="62" t="n"/>
+      <c r="O78" s="61" t="n"/>
+      <c r="P78" s="62" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="D69:N69"/>
-    <mergeCell ref="H78:L78"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="D1:N1"/>
-    <mergeCell ref="D63:N63"/>
+  <mergeCells count="33">
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E1:P1"/>
+    <mergeCell ref="E63:P63"/>
+    <mergeCell ref="E69:P69"/>
+    <mergeCell ref="E60:P60"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E65:P65"/>
     <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="N71:N74"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="E71:M74"/>
-    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="E61:P61"/>
+    <mergeCell ref="E70:P70"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="D75:N77"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E66:P66"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E75:P77"/>
     <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D68:N68"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D67:N67"/>
+    <mergeCell ref="E68:P68"/>
+    <mergeCell ref="F71:O74"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="P71:P74"/>
+    <mergeCell ref="E62:P62"/>
+    <mergeCell ref="E67:P67"/>
+    <mergeCell ref="E64:P64"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="D59:D60"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
